--- a/Result/profitability/8935.xlsx
+++ b/Result/profitability/8935.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.23</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.18375</v>
+        <v>-0.16375</v>
       </c>
       <c r="N2" t="n">
-        <v>10.77</v>
+        <v>11.61375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.17875</v>
+        <v>-0.17125</v>
       </c>
       <c r="N3" t="n">
-        <v>10.275</v>
+        <v>10.4125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.44</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2162500000000001</v>
+        <v>-0.19875</v>
       </c>
       <c r="N4" t="n">
-        <v>8.9475</v>
+        <v>9.442499999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-4.09</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7000000000000001</v>
+        <v>-0.69125</v>
       </c>
       <c r="N5" t="n">
-        <v>4.0275</v>
+        <v>4.38</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.67625</v>
+        <v>-0.6625</v>
       </c>
       <c r="N6" t="n">
-        <v>4.345</v>
+        <v>5.2075</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6562500000000001</v>
+        <v>-0.64</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6325</v>
+        <v>4.9475</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.22</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6575000000000001</v>
+        <v>-0.65625</v>
       </c>
       <c r="N8" t="n">
-        <v>4.16375</v>
+        <v>3.7725</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>-1.99</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8950000000000001</v>
+        <v>-0.895</v>
       </c>
       <c r="N9" t="n">
         <v>0.4824999999999999</v>
@@ -1899,7 +1899,7 @@
         <v>0.01</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7725000000000001</v>
+        <v>-0.7725</v>
       </c>
       <c r="N12" t="n">
         <v>7.41625</v>
@@ -2026,7 +2026,7 @@
         <v>-0.45</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3175000000000001</v>
+        <v>-0.3175</v>
       </c>
       <c r="N13" t="n">
         <v>11.1875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8935</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>114</v>
+      </c>
+      <c r="D75" t="n">
+        <v>97</v>
+      </c>
+      <c r="E75" t="n">
+        <v>16</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-10.08%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-11</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.165</v>
+      </c>
+      <c r="N75" t="n">
+        <v>11.745</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.009999999999999995</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.111111111111111</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.129999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1789594053744997</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.06999999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2443674176776429</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
